--- a/tabtools/qa/baseline/workbooks/survtab_km.xlsx
+++ b/tabtools/qa/baseline/workbooks/survtab_km.xlsx
@@ -94,7 +94,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="172">
+  <fonts count="180">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -684,6 +684,38 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -810,7 +842,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="119">
+  <borders count="127">
     <border>
       <left/>
       <right/>
@@ -1614,11 +1646,67 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -2075,6 +2163,38 @@
     </xf>
     <xf numFmtId="0" fontId="171" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2253,22 +2373,23 @@
       <c r="A10" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="116" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="117" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="118" t="s">
+      <c r="C10" s="123" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="123" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="123" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B10:E10"/>
   </mergeCells>
 </worksheet>
 </file>